--- a/hardware/inventory.xlsx
+++ b/hardware/inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mark\Desktop\PocketLab\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69B46F3-4C31-44CD-B171-AB5DB033DB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC13D22-5FE6-416B-8A36-41FD1355956D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="162" yWindow="1494" windowWidth="20430" windowHeight="10656" xr2:uid="{26A4A25A-C883-41FE-97F5-F66743B7E37E}"/>
+    <workbookView xWindow="2610" yWindow="2538" windowWidth="20430" windowHeight="9984" xr2:uid="{26A4A25A-C883-41FE-97F5-F66743B7E37E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="420">
   <si>
     <t>MFG#</t>
   </si>
@@ -729,6 +729,576 @@
   </si>
   <si>
     <t>Function Generator</t>
+  </si>
+  <si>
+    <t>Analog Parts Kit</t>
+  </si>
+  <si>
+    <t>AD8226</t>
+  </si>
+  <si>
+    <t>Instrumentation amplifier (breakout board)</t>
+  </si>
+  <si>
+    <t>ADTL082</t>
+  </si>
+  <si>
+    <t>JFET operational amplifier (breakout board)</t>
+  </si>
+  <si>
+    <t>AD8542</t>
+  </si>
+  <si>
+    <t>CMOS rail-to-rail operational amplifier (breakout board)</t>
+  </si>
+  <si>
+    <t>OP482</t>
+  </si>
+  <si>
+    <t>High-speed JFET operational amplifier, 14-lead PDIP</t>
+  </si>
+  <si>
+    <t>Precision rail-to-rail input/output operational amplifier, 14-lead PDIP</t>
+  </si>
+  <si>
+    <t>OP27</t>
+  </si>
+  <si>
+    <t>Low-noise precision operational amplifier, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>OP37</t>
+  </si>
+  <si>
+    <t>Precision operational amplifier, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>OP97</t>
+  </si>
+  <si>
+    <t>Low-power high-precision operational amplifier, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>LTC1541</t>
+  </si>
+  <si>
+    <t>Micropower amplifier, comparator, and reference (breakout board)</t>
+  </si>
+  <si>
+    <t>AD8210</t>
+  </si>
+  <si>
+    <t>Current-shunt monitor (breakout board)</t>
+  </si>
+  <si>
+    <t>AD22151</t>
+  </si>
+  <si>
+    <t>Magnetic-field sensor (breakout board)</t>
+  </si>
+  <si>
+    <t>ADXL327</t>
+  </si>
+  <si>
+    <t>3-axis accelerometer (breakout board)</t>
+  </si>
+  <si>
+    <t>AD22100</t>
+  </si>
+  <si>
+    <t>Voltage-output temperature sensor, TO-92</t>
+  </si>
+  <si>
+    <t>AD592</t>
+  </si>
+  <si>
+    <t>Current-output temperature sensor, TO-92</t>
+  </si>
+  <si>
+    <t>TMP01</t>
+  </si>
+  <si>
+    <t>Temperature controller, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>Electret microphone</t>
+  </si>
+  <si>
+    <t>10 kΩ thermistor</t>
+  </si>
+  <si>
+    <t>Thermistor, 10 kΩ</t>
+  </si>
+  <si>
+    <t>OP999</t>
+  </si>
+  <si>
+    <t>PIN photodiode</t>
+  </si>
+  <si>
+    <t>ADP3300</t>
+  </si>
+  <si>
+    <t>3.3 V, 50 mA LDO linear regulator (breakout board)</t>
+  </si>
+  <si>
+    <t>LT3092</t>
+  </si>
+  <si>
+    <t>Programmable current source (breakout board)</t>
+  </si>
+  <si>
+    <t>LTM8067</t>
+  </si>
+  <si>
+    <t>Isolated DC-to-DC converter (breakout board)</t>
+  </si>
+  <si>
+    <t>LT3080</t>
+  </si>
+  <si>
+    <t>Adjustable 1.1 A LDO regulator, TO-220</t>
+  </si>
+  <si>
+    <t>LTC1054</t>
+  </si>
+  <si>
+    <t>Switched-capacitor regulator, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>AD654</t>
+  </si>
+  <si>
+    <t>Voltage-to-frequency converter, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>12-bit nanoDAC+ (breakout board)</t>
+  </si>
+  <si>
+    <t>AD7091R-5</t>
+  </si>
+  <si>
+    <t>12-bit 4-channel I²C ADC (breakout board)</t>
+  </si>
+  <si>
+    <t>AD584</t>
+  </si>
+  <si>
+    <t>Programmable voltage reference, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>AD8561</t>
+  </si>
+  <si>
+    <t>Comparator, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>LTC1485</t>
+  </si>
+  <si>
+    <t>Differential bus transceiver, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>LTC1043</t>
+  </si>
+  <si>
+    <t>Precision switched-capacitor building block, 8-lead PDIP</t>
+  </si>
+  <si>
+    <t>Resistor 1.1 Ω</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 1.1 Ω</t>
+  </si>
+  <si>
+    <t>Resistor 10 Ω</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 10 Ω</t>
+  </si>
+  <si>
+    <t>Resistor 47 Ω</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 47 Ω</t>
+  </si>
+  <si>
+    <t>Resistor 68 Ω</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 68 Ω</t>
+  </si>
+  <si>
+    <t>Resistor 100 Ω</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 100 Ω</t>
+  </si>
+  <si>
+    <t>Resistor 470 Ω</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 470 Ω</t>
+  </si>
+  <si>
+    <t>Resistor 1 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 1 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 1.5 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 1.5 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 2.2 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 2.2 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 4.7 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 4.7 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 6.8 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 6.8 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 10 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 10 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 20 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 20 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 47 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 47 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 68 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 68 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 100 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 100 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 200 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 200 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 470 kΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 470 kΩ</t>
+  </si>
+  <si>
+    <t>Resistor 1 MΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 1 MΩ</t>
+  </si>
+  <si>
+    <t>Resistor 5 MΩ</t>
+  </si>
+  <si>
+    <t>Through-hole resistor, 5 MΩ</t>
+  </si>
+  <si>
+    <t>Power resistor 6.2 Ω</t>
+  </si>
+  <si>
+    <t>Power resistor, 6.2 Ω, 10 W</t>
+  </si>
+  <si>
+    <t>Potentiometer 5 kΩ</t>
+  </si>
+  <si>
+    <t>Potentiometer, 5 kΩ</t>
+  </si>
+  <si>
+    <t>Potentiometer 10 kΩ</t>
+  </si>
+  <si>
+    <t>Potentiometer, 10 kΩ</t>
+  </si>
+  <si>
+    <t>Potentiometer 50 kΩ</t>
+  </si>
+  <si>
+    <t>Potentiometer, 50 kΩ</t>
+  </si>
+  <si>
+    <t>Capacitor 39 pF</t>
+  </si>
+  <si>
+    <t>Capacitor, 39 pF</t>
+  </si>
+  <si>
+    <t>Capacitor 100 pF</t>
+  </si>
+  <si>
+    <t>Capacitor, 100 pF</t>
+  </si>
+  <si>
+    <t>Capacitor 0.001 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 0.001 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 0.0047 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 0.0047 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 0.01 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 0.01 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 0.047 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 0.047 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 0.1 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 0.1 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 1 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 1 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 4.7 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 4.7 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 10 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 10 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 22 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 22 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 47 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 47 µF</t>
+  </si>
+  <si>
+    <t>Capacitor 220 µF</t>
+  </si>
+  <si>
+    <t>Capacitor, 220 µF</t>
+  </si>
+  <si>
+    <t>2N3904</t>
+  </si>
+  <si>
+    <t>Small-signal NPN transistor</t>
+  </si>
+  <si>
+    <t>2N3906</t>
+  </si>
+  <si>
+    <t>Small-signal PNP transistor</t>
+  </si>
+  <si>
+    <t>IRF510</t>
+  </si>
+  <si>
+    <t>Power MOSFET</t>
+  </si>
+  <si>
+    <t>TIP31CFS</t>
+  </si>
+  <si>
+    <t>NPN power transistor</t>
+  </si>
+  <si>
+    <t>TIP32CFS</t>
+  </si>
+  <si>
+    <t>PNP power transistor</t>
+  </si>
+  <si>
+    <t>ZVN2110A</t>
+  </si>
+  <si>
+    <t>N-channel DMOS FET</t>
+  </si>
+  <si>
+    <t>ZVN3310</t>
+  </si>
+  <si>
+    <t>ZVP2110A</t>
+  </si>
+  <si>
+    <t>P-channel MOSFET</t>
+  </si>
+  <si>
+    <t>SN74HC08</t>
+  </si>
+  <si>
+    <t>Quad AND gate, 14-lead PDIP</t>
+  </si>
+  <si>
+    <t>SN74HC32</t>
+  </si>
+  <si>
+    <t>Quad OR gate, 14-lead PDIP</t>
+  </si>
+  <si>
+    <t>SN74HC273</t>
+  </si>
+  <si>
+    <t>Octal flip-flop, 14-lead PDIP</t>
+  </si>
+  <si>
+    <t>SN74HC04</t>
+  </si>
+  <si>
+    <t>Hex inverter, 14-lead PDIP</t>
+  </si>
+  <si>
+    <t>Green LED</t>
+  </si>
+  <si>
+    <t>Yellow LED</t>
+  </si>
+  <si>
+    <t>Red LED</t>
+  </si>
+  <si>
+    <t>QED123</t>
+  </si>
+  <si>
+    <t>Infrared LED</t>
+  </si>
+  <si>
+    <t>QSD123</t>
+  </si>
+  <si>
+    <t>Infrared phototransistor</t>
+  </si>
+  <si>
+    <t>1N3064</t>
+  </si>
+  <si>
+    <t>Small-signal diode</t>
+  </si>
+  <si>
+    <t>General-purpose plastic rectifier diode</t>
+  </si>
+  <si>
+    <t>1N4735</t>
+  </si>
+  <si>
+    <t>1 W Zener diode</t>
+  </si>
+  <si>
+    <t>Fast-switching diode</t>
+  </si>
+  <si>
+    <t>RFB0807-1R0L</t>
+  </si>
+  <si>
+    <t>Inductor, 1.0 µH</t>
+  </si>
+  <si>
+    <t>RFB0807-100L</t>
+  </si>
+  <si>
+    <t>Inductor, 10 µH</t>
+  </si>
+  <si>
+    <t>RFB0807-101L</t>
+  </si>
+  <si>
+    <t>Inductor, 100 µH</t>
+  </si>
+  <si>
+    <t>RFB0807-102L</t>
+  </si>
+  <si>
+    <t>Inductor, 1 mH</t>
+  </si>
+  <si>
+    <t>RFB0807-103L</t>
+  </si>
+  <si>
+    <t>Inductor, 10 mH</t>
+  </si>
+  <si>
+    <t>HPH1-1400L</t>
+  </si>
+  <si>
+    <t>Hexa-Path magnetics component (breakout board)</t>
+  </si>
+  <si>
+    <t>HPH1-0190L</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>Solderless breadboard</t>
+  </si>
+  <si>
+    <t>Flathead screwdriver</t>
+  </si>
+  <si>
+    <t>USB connector</t>
+  </si>
+  <si>
+    <t>USB connector (breakout board)</t>
+  </si>
+  <si>
+    <t>Audio connector</t>
+  </si>
+  <si>
+    <t>Audio connector (breakout board)</t>
+  </si>
+  <si>
+    <t>Jumper wires</t>
+  </si>
+  <si>
+    <t>Jumper wires with pin ends</t>
   </si>
 </sst>
 </file>
@@ -803,9 +1373,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1151,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D28C7C-4E93-445C-B5C8-CB3D69E06964}">
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="19.734375" customWidth="1"/>
@@ -1163,221 +1732,213 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1394,7 +1955,7 @@
       <c r="D12" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1411,7 +1972,7 @@
       <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1428,7 +1989,7 @@
       <c r="D14" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1445,7 +2006,7 @@
       <c r="D15" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1462,7 +2023,7 @@
       <c r="D16" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1479,7 +2040,7 @@
       <c r="D17" t="s">
         <v>62</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1496,7 +2057,7 @@
       <c r="D18" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1513,7 +2074,7 @@
       <c r="D19" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1530,7 +2091,7 @@
       <c r="D20" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1547,1856 +2108,3703 @@
       <c r="D21" t="s">
         <v>65</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="23.4">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>68</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D22" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="7">
+      <c r="A27" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="6">
         <v>15</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="7">
+      <c r="A28" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="6">
         <v>15</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="7">
+      <c r="A29" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="6">
         <v>15</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="7">
+      <c r="A30" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="6">
         <v>15</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="7">
+      <c r="A31" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="6">
         <v>15</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="7">
+      <c r="A32" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="6">
         <v>15</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="7">
+      <c r="A33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="6">
         <v>15</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="7">
+      <c r="A34" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="6">
         <v>15</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="7">
+      <c r="A35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="6">
         <v>15</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="7">
+      <c r="A36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="6">
         <v>15</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="7">
+      <c r="A37" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="6">
         <v>15</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" s="7">
+      <c r="A38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="6">
         <v>15</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="7">
+      <c r="A39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="6">
         <v>20</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="7">
+      <c r="A40" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="6">
         <v>20</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="7">
+      <c r="A41" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="6">
         <v>20</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="7">
+      <c r="A42" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="6">
         <v>20</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" s="7">
+      <c r="A43" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="6">
         <v>20</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="7">
+      <c r="A44" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="6">
         <v>20</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="7">
+      <c r="A45" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="6">
         <v>20</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="7">
+      <c r="A46" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="6">
         <v>20</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B47" s="7">
+      <c r="A47" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="6">
         <v>20</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="7">
+      <c r="A48" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="6">
         <v>20</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" s="7">
+      <c r="A49" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="6">
         <v>20</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B50" s="7">
+      <c r="A50" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="6">
         <v>20</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B51" s="7">
+      <c r="A51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="6">
         <v>20</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" s="7">
+      <c r="A52" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="6">
         <v>20</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="7">
+      <c r="A53" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="6">
         <v>20</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" s="7">
+      <c r="A54" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="6">
         <v>20</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" s="7">
+      <c r="A55" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="6">
         <v>20</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="7">
+      <c r="A56" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="6">
         <v>20</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" s="7">
+      <c r="A57" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="6">
         <v>20</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="7">
+      <c r="A58" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="6">
         <v>20</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="7">
+      <c r="A59" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="6">
         <v>20</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B60" s="7">
+      <c r="A60" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="6">
         <v>20</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" s="7">
+      <c r="A61" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6">
         <v>20</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="6" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B62" s="7">
+      <c r="A62" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="6">
         <v>20</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B63" s="7">
+      <c r="A63" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" s="6">
         <v>20</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B64" s="7">
+      <c r="A64" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="6">
         <v>20</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="7">
+      <c r="A65" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="6">
         <v>20</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="7">
+      <c r="A66" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="6">
         <v>20</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="7">
+      <c r="A67" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="6">
         <v>20</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="6" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B68" s="7">
+      <c r="A68" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="6">
         <v>20</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="6" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B69" s="7">
+      <c r="A69" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="6">
         <v>20</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="7">
+      <c r="A70" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70" s="6">
         <v>20</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B71" s="7">
+      <c r="A71" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="6">
         <v>20</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B72" s="7">
+      <c r="A72" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B72" s="6">
         <v>20</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B73" s="7">
+      <c r="A73" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="6">
         <v>20</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B74" s="7">
+      <c r="A74" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6">
         <v>20</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="7">
+      <c r="A75" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="6">
         <v>15</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B76" s="7">
+      <c r="A76" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="6">
         <v>15</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="6" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B77" s="7">
+      <c r="A77" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B77" s="6">
         <v>15</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B78" s="7">
+      <c r="A78" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B78" s="6">
         <v>15</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B79" s="7">
+      <c r="A79" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B79" s="6">
         <v>15</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="6" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B80" s="7">
+      <c r="A80" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B80" s="6">
         <v>15</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="6" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B81" s="7">
+      <c r="A81" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B81" s="6">
         <v>15</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="6" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B82" s="7">
+      <c r="A82" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B82" s="6">
         <v>15</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B83" s="7">
+      <c r="A83" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83" s="6">
         <v>15</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="6" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B84" s="7">
+      <c r="A84" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" s="6">
         <v>15</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B85" s="7">
+      <c r="A85" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85" s="6">
         <v>15</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B86" s="7">
+      <c r="A86" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="6">
         <v>15</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B87" s="7">
+      <c r="A87" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" s="6">
         <v>15</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="6" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="3" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B92" s="7">
-        <v>10</v>
-      </c>
-      <c r="C92" s="7" t="s">
+      <c r="B92" s="6">
+        <v>10</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="D92" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B93" s="7">
-        <v>10</v>
-      </c>
-      <c r="C93" s="7" t="s">
+      <c r="B93" s="6">
+        <v>10</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B94" s="7">
-        <v>10</v>
-      </c>
-      <c r="C94" s="7" t="s">
+      <c r="B94" s="6">
+        <v>10</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B95" s="7">
-        <v>10</v>
-      </c>
-      <c r="C95" s="7" t="s">
+      <c r="B95" s="6">
+        <v>10</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="D95" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B96" s="7">
-        <v>10</v>
-      </c>
-      <c r="C96" s="7" t="s">
+      <c r="B96" s="6">
+        <v>10</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="D96" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B97" s="7">
-        <v>10</v>
-      </c>
-      <c r="C97" s="7" t="s">
+      <c r="B97" s="6">
+        <v>10</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B98" s="7">
-        <v>10</v>
-      </c>
-      <c r="C98" s="7" t="s">
+      <c r="B98" s="6">
+        <v>10</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B99" s="7">
-        <v>10</v>
-      </c>
-      <c r="C99" s="7" t="s">
+      <c r="B99" s="6">
+        <v>10</v>
+      </c>
+      <c r="C99" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B100" s="7">
-        <v>10</v>
-      </c>
-      <c r="C100" s="7" t="s">
+      <c r="B100" s="6">
+        <v>10</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B101" s="7">
-        <v>10</v>
-      </c>
-      <c r="C101" s="7" t="s">
+      <c r="B101" s="6">
+        <v>10</v>
+      </c>
+      <c r="C101" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B102" s="7">
-        <v>10</v>
-      </c>
-      <c r="C102" s="7" t="s">
+      <c r="B102" s="6">
+        <v>10</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="D102" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B103" s="7">
-        <v>10</v>
-      </c>
-      <c r="C103" s="7" t="s">
+      <c r="B103" s="6">
+        <v>10</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="D103" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B104" s="7">
-        <v>10</v>
-      </c>
-      <c r="C104" s="7" t="s">
+      <c r="B104" s="6">
+        <v>10</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="D104" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B105" s="7">
-        <v>10</v>
-      </c>
-      <c r="C105" s="7" t="s">
+      <c r="B105" s="6">
+        <v>10</v>
+      </c>
+      <c r="C105" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D105" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B106" s="7">
-        <v>10</v>
-      </c>
-      <c r="C106" s="7" t="s">
+      <c r="B106" s="6">
+        <v>10</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="D106" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B107" s="7">
-        <v>10</v>
-      </c>
-      <c r="C107" s="7" t="s">
+      <c r="B107" s="6">
+        <v>10</v>
+      </c>
+      <c r="C107" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D107" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B108" s="7">
-        <v>10</v>
-      </c>
-      <c r="C108" s="7" t="s">
+      <c r="B108" s="6">
+        <v>10</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B109" s="7">
-        <v>10</v>
-      </c>
-      <c r="C109" s="7" t="s">
+      <c r="B109" s="6">
+        <v>10</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="6">
         <v>5</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D110" s="8" t="s">
+      <c r="D110" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="6">
         <v>5</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D111" s="8" t="s">
+      <c r="D111" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="6">
         <v>100</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D112" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="7" t="s">
+      <c r="A115" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="E115" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="F115" s="6" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="7" t="s">
+      <c r="A116" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B116" s="7">
-        <v>10</v>
-      </c>
-      <c r="C116" s="7" t="s">
+      <c r="B116" s="6">
+        <v>10</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7">
+      <c r="D116" s="6"/>
+      <c r="E116" s="6">
         <v>100</v>
       </c>
-      <c r="F116" s="7"/>
+      <c r="F116" s="6"/>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="7" t="s">
+      <c r="A117" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B117" s="7">
-        <v>10</v>
-      </c>
-      <c r="C117" s="7" t="s">
+      <c r="B117" s="6">
+        <v>10</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7">
+      <c r="D117" s="6"/>
+      <c r="E117" s="6">
         <v>200</v>
       </c>
-      <c r="F117" s="7"/>
+      <c r="F117" s="6"/>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="7" t="s">
+      <c r="A118" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B118" s="7">
-        <v>10</v>
-      </c>
-      <c r="C118" s="7" t="s">
+      <c r="B118" s="6">
+        <v>10</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7">
+      <c r="D118" s="6"/>
+      <c r="E118" s="6">
         <v>300</v>
       </c>
-      <c r="F118" s="7"/>
+      <c r="F118" s="6"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="7" t="s">
+      <c r="A119" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B119" s="7">
-        <v>10</v>
-      </c>
-      <c r="C119" s="7" t="s">
+      <c r="B119" s="6">
+        <v>10</v>
+      </c>
+      <c r="C119" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7">
+      <c r="D119" s="6"/>
+      <c r="E119" s="6">
         <v>470</v>
       </c>
-      <c r="F119" s="7"/>
+      <c r="F119" s="6"/>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="7" t="s">
+      <c r="A120" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B120" s="7">
-        <v>10</v>
-      </c>
-      <c r="C120" s="7" t="s">
+      <c r="B120" s="6">
+        <v>10</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7">
+      <c r="D120" s="6"/>
+      <c r="E120" s="6">
         <v>560</v>
       </c>
-      <c r="F120" s="7"/>
+      <c r="F120" s="6"/>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="7" t="s">
+      <c r="A121" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B121" s="7">
-        <v>10</v>
-      </c>
-      <c r="C121" s="7" t="s">
+      <c r="B121" s="6">
+        <v>10</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7">
+      <c r="D121" s="6"/>
+      <c r="E121" s="6">
         <v>680</v>
       </c>
-      <c r="F121" s="7"/>
+      <c r="F121" s="6"/>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="7" t="s">
+      <c r="A122" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B122" s="7">
-        <v>10</v>
-      </c>
-      <c r="C122" s="7" t="s">
+      <c r="B122" s="6">
+        <v>10</v>
+      </c>
+      <c r="C122" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7">
+      <c r="D122" s="6"/>
+      <c r="E122" s="6">
         <v>101</v>
       </c>
-      <c r="F122" s="7"/>
+      <c r="F122" s="6"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="7" t="s">
+      <c r="A123" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B123" s="7">
-        <v>10</v>
-      </c>
-      <c r="C123" s="7" t="s">
+      <c r="B123" s="6">
+        <v>10</v>
+      </c>
+      <c r="C123" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7">
+      <c r="D123" s="6"/>
+      <c r="E123" s="6">
         <v>221</v>
       </c>
-      <c r="F123" s="7"/>
+      <c r="F123" s="6"/>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B124" s="7">
-        <v>10</v>
-      </c>
-      <c r="C124" s="7" t="s">
+      <c r="B124" s="6">
+        <v>10</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7">
+      <c r="D124" s="6"/>
+      <c r="E124" s="6">
         <v>331</v>
       </c>
-      <c r="F124" s="7"/>
+      <c r="F124" s="6"/>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="7" t="s">
+      <c r="A125" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B125" s="7">
-        <v>10</v>
-      </c>
-      <c r="C125" s="7" t="s">
+      <c r="B125" s="6">
+        <v>10</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7">
+      <c r="D125" s="6"/>
+      <c r="E125" s="6">
         <v>681</v>
       </c>
-      <c r="F125" s="7"/>
+      <c r="F125" s="6"/>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="7" t="s">
+      <c r="A126" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B126" s="7">
-        <v>10</v>
-      </c>
-      <c r="C126" s="7" t="s">
+      <c r="B126" s="6">
+        <v>10</v>
+      </c>
+      <c r="C126" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7">
+      <c r="D126" s="6"/>
+      <c r="E126" s="6">
         <v>102</v>
       </c>
-      <c r="F126" s="7"/>
+      <c r="F126" s="6"/>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B127" s="7">
-        <v>10</v>
-      </c>
-      <c r="C127" s="7" t="s">
+      <c r="B127" s="6">
+        <v>10</v>
+      </c>
+      <c r="C127" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7">
+      <c r="D127" s="6"/>
+      <c r="E127" s="6">
         <v>472</v>
       </c>
-      <c r="F127" s="7"/>
+      <c r="F127" s="6"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="7" t="s">
+      <c r="A128" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B128" s="7">
-        <v>10</v>
-      </c>
-      <c r="C128" s="7" t="s">
+      <c r="B128" s="6">
+        <v>10</v>
+      </c>
+      <c r="C128" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7">
+      <c r="D128" s="6"/>
+      <c r="E128" s="6">
         <v>103</v>
       </c>
-      <c r="F128" s="7"/>
+      <c r="F128" s="6"/>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="7" t="s">
+      <c r="A129" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B129" s="7">
-        <v>10</v>
-      </c>
-      <c r="C129" s="7" t="s">
+      <c r="B129" s="6">
+        <v>10</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7">
+      <c r="D129" s="6"/>
+      <c r="E129" s="6">
         <v>473</v>
       </c>
-      <c r="F129" s="7"/>
+      <c r="F129" s="6"/>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B130" s="7">
-        <v>10</v>
-      </c>
-      <c r="C130" s="7" t="s">
+      <c r="B130" s="6">
+        <v>10</v>
+      </c>
+      <c r="C130" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7">
+      <c r="D130" s="6"/>
+      <c r="E130" s="6">
         <v>104</v>
       </c>
-      <c r="F130" s="7"/>
+      <c r="F130" s="6"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B131" s="7">
-        <v>10</v>
-      </c>
-      <c r="C131" s="7" t="s">
+      <c r="B131" s="6">
+        <v>10</v>
+      </c>
+      <c r="C131" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7">
+      <c r="D131" s="6"/>
+      <c r="E131" s="6">
         <v>154</v>
       </c>
-      <c r="F131" s="7"/>
+      <c r="F131" s="6"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="7" t="s">
+      <c r="A132" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B132" s="7">
-        <v>10</v>
-      </c>
-      <c r="C132" s="7" t="s">
+      <c r="B132" s="6">
+        <v>10</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7">
+      <c r="D132" s="6"/>
+      <c r="E132" s="6">
         <v>224</v>
       </c>
-      <c r="F132" s="7"/>
+      <c r="F132" s="6"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="7" t="s">
+      <c r="A133" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B133" s="7">
-        <v>10</v>
-      </c>
-      <c r="C133" s="7" t="s">
+      <c r="B133" s="6">
+        <v>10</v>
+      </c>
+      <c r="C133" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7">
+      <c r="D133" s="6"/>
+      <c r="E133" s="6">
         <v>334</v>
       </c>
-      <c r="F133" s="7"/>
+      <c r="F133" s="6"/>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="7" t="s">
+      <c r="A134" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B134" s="7">
-        <v>10</v>
-      </c>
-      <c r="C134" s="7" t="s">
+      <c r="B134" s="6">
+        <v>10</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7">
+      <c r="D134" s="6"/>
+      <c r="E134" s="6">
         <v>474</v>
       </c>
-      <c r="F134" s="7"/>
+      <c r="F134" s="6"/>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="7" t="s">
+      <c r="A135" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B135" s="7">
-        <v>10</v>
-      </c>
-      <c r="C135" s="7" t="s">
+      <c r="B135" s="6">
+        <v>10</v>
+      </c>
+      <c r="C135" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7">
+      <c r="D135" s="6"/>
+      <c r="E135" s="6">
         <v>684</v>
       </c>
-      <c r="F135" s="7"/>
+      <c r="F135" s="6"/>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B136" s="7">
-        <v>10</v>
-      </c>
-      <c r="C136" s="7" t="s">
+      <c r="B136" s="6">
+        <v>10</v>
+      </c>
+      <c r="C136" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7">
+      <c r="D136" s="6"/>
+      <c r="E136" s="6">
         <v>105</v>
       </c>
-      <c r="F136" s="7"/>
+      <c r="F136" s="6"/>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="7" t="s">
+      <c r="A137" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B137" s="7">
-        <v>10</v>
-      </c>
-      <c r="C137" s="7" t="s">
+      <c r="B137" s="6">
+        <v>10</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7">
+      <c r="D137" s="6"/>
+      <c r="E137" s="6">
         <v>225</v>
       </c>
-      <c r="F137" s="7"/>
+      <c r="F137" s="6"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="7" t="s">
+      <c r="A138" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B138" s="7">
-        <v>10</v>
-      </c>
-      <c r="C138" s="7" t="s">
+      <c r="B138" s="6">
+        <v>10</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7">
+      <c r="D138" s="6"/>
+      <c r="E138" s="6">
         <v>475</v>
       </c>
-      <c r="F138" s="7"/>
+      <c r="F138" s="6"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="7" t="s">
+      <c r="A139" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B139" s="7">
-        <v>10</v>
-      </c>
-      <c r="C139" s="7" t="s">
+      <c r="B139" s="6">
+        <v>10</v>
+      </c>
+      <c r="C139" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7">
+      <c r="D139" s="6"/>
+      <c r="E139" s="6">
         <v>106</v>
       </c>
-      <c r="F139" s="7"/>
+      <c r="F139" s="6"/>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B140" s="7">
-        <v>10</v>
-      </c>
-      <c r="C140" s="7" t="s">
+      <c r="B140" s="6">
+        <v>10</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7" t="s">
+      <c r="E140" s="6"/>
+      <c r="F140" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="7" t="s">
+      <c r="A141" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B141" s="7">
-        <v>10</v>
-      </c>
-      <c r="C141" s="7" t="s">
+      <c r="B141" s="6">
+        <v>10</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D141" s="7" t="s">
+      <c r="D141" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7" t="s">
+      <c r="E141" s="6"/>
+      <c r="F141" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="7" t="s">
+      <c r="A142" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B142" s="7">
-        <v>10</v>
-      </c>
-      <c r="C142" s="7" t="s">
+      <c r="B142" s="6">
+        <v>10</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="D142" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7" t="s">
+      <c r="E142" s="6"/>
+      <c r="F142" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="7" t="s">
+      <c r="A143" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B143" s="7">
-        <v>10</v>
-      </c>
-      <c r="C143" s="7" t="s">
+      <c r="B143" s="6">
+        <v>10</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="D143" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7" t="s">
+      <c r="E143" s="6"/>
+      <c r="F143" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="7" t="s">
+      <c r="A144" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B144" s="7">
-        <v>10</v>
-      </c>
-      <c r="C144" s="7" t="s">
+      <c r="B144" s="6">
+        <v>10</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="D144" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7" t="s">
+      <c r="E144" s="6"/>
+      <c r="F144" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="145" spans="1:6">
-      <c r="A145" s="7" t="s">
+      <c r="A145" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B145" s="7">
-        <v>10</v>
-      </c>
-      <c r="C145" s="7" t="s">
+      <c r="B145" s="6">
+        <v>10</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="D145" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E145" s="7"/>
-      <c r="F145" s="7" t="s">
+      <c r="E145" s="6"/>
+      <c r="F145" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="146" spans="1:6">
-      <c r="A146" s="7" t="s">
+      <c r="A146" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B146" s="7">
-        <v>10</v>
-      </c>
-      <c r="C146" s="7" t="s">
+      <c r="B146" s="6">
+        <v>10</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7" t="s">
+      <c r="E146" s="6"/>
+      <c r="F146" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="147" spans="1:6">
-      <c r="A147" s="7" t="s">
+      <c r="A147" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B147" s="7">
-        <v>10</v>
-      </c>
-      <c r="C147" s="7" t="s">
+      <c r="B147" s="6">
+        <v>10</v>
+      </c>
+      <c r="C147" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="D147" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E147" s="7"/>
-      <c r="F147" s="7" t="s">
+      <c r="E147" s="6"/>
+      <c r="F147" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="148" spans="1:6">
-      <c r="A148" s="7" t="s">
+      <c r="A148" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B148" s="7">
-        <v>10</v>
-      </c>
-      <c r="C148" s="7" t="s">
+      <c r="B148" s="6">
+        <v>10</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="D148" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7" t="s">
+      <c r="E148" s="6"/>
+      <c r="F148" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="149" spans="1:6">
-      <c r="A149" s="7" t="s">
+      <c r="A149" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B149" s="7">
-        <v>10</v>
-      </c>
-      <c r="C149" s="7" t="s">
+      <c r="B149" s="6">
+        <v>10</v>
+      </c>
+      <c r="C149" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="D149" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E149" s="7"/>
-      <c r="F149" s="7" t="s">
+      <c r="E149" s="6"/>
+      <c r="F149" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B150" s="7">
-        <v>10</v>
-      </c>
-      <c r="C150" s="7" t="s">
+      <c r="B150" s="6">
+        <v>10</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E150" s="7"/>
-      <c r="F150" s="7" t="s">
+      <c r="E150" s="6"/>
+      <c r="F150" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:6">
-      <c r="A151" s="7" t="s">
+      <c r="A151" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B151" s="7">
-        <v>10</v>
-      </c>
-      <c r="C151" s="7" t="s">
+      <c r="B151" s="6">
+        <v>10</v>
+      </c>
+      <c r="C151" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="D151" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7" t="s">
+      <c r="E151" s="6"/>
+      <c r="F151" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="7" t="s">
+      <c r="A152" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B152" s="7">
-        <v>10</v>
-      </c>
-      <c r="C152" s="7" t="s">
+      <c r="B152" s="6">
+        <v>10</v>
+      </c>
+      <c r="C152" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="D152" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7" t="s">
+      <c r="E152" s="6"/>
+      <c r="F152" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:6">
-      <c r="A153" s="7" t="s">
+      <c r="A153" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B153" s="7">
-        <v>10</v>
-      </c>
-      <c r="C153" s="7" t="s">
+      <c r="B153" s="6">
+        <v>10</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="D153" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E153" s="7"/>
-      <c r="F153" s="7" t="s">
+      <c r="E153" s="6"/>
+      <c r="F153" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:6">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B154" s="7">
-        <v>10</v>
-      </c>
-      <c r="C154" s="7" t="s">
+      <c r="B154" s="6">
+        <v>10</v>
+      </c>
+      <c r="C154" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D154" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7" t="s">
+      <c r="E154" s="6"/>
+      <c r="F154" s="6" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="7" t="s">
+      <c r="A155" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B155" s="7">
-        <v>10</v>
-      </c>
-      <c r="C155" s="7" t="s">
+      <c r="B155" s="6">
+        <v>10</v>
+      </c>
+      <c r="C155" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="D155" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E155" s="7"/>
-      <c r="F155" s="7" t="s">
+      <c r="E155" s="6"/>
+      <c r="F155" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B156" s="7">
-        <v>10</v>
-      </c>
-      <c r="C156" s="7" t="s">
+      <c r="B156" s="6">
+        <v>10</v>
+      </c>
+      <c r="C156" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="D156" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7" t="s">
+      <c r="E156" s="6"/>
+      <c r="F156" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="7" t="s">
+      <c r="A157" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B157" s="7">
-        <v>10</v>
-      </c>
-      <c r="C157" s="7" t="s">
+      <c r="B157" s="6">
+        <v>10</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="D157" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7" t="s">
+      <c r="E157" s="6"/>
+      <c r="F157" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="7" t="s">
+      <c r="A158" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B158" s="7">
-        <v>10</v>
-      </c>
-      <c r="C158" s="7" t="s">
+      <c r="B158" s="6">
+        <v>10</v>
+      </c>
+      <c r="C158" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7" t="s">
+      <c r="E158" s="6"/>
+      <c r="F158" s="6" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="7" t="s">
+      <c r="A159" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B159" s="7">
-        <v>10</v>
-      </c>
-      <c r="C159" s="7" t="s">
+      <c r="B159" s="6">
+        <v>10</v>
+      </c>
+      <c r="C159" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="D159" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7" t="s">
+      <c r="E159" s="6"/>
+      <c r="F159" s="6" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B160" s="7">
-        <v>10</v>
-      </c>
-      <c r="C160" s="7" t="s">
+      <c r="B160" s="6">
+        <v>10</v>
+      </c>
+      <c r="C160" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="D160" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7" t="s">
+      <c r="E160" s="6"/>
+      <c r="F160" s="6" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="A161" s="7" t="s">
+    <row r="161" spans="1:8">
+      <c r="A161" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B161" s="7">
-        <v>10</v>
-      </c>
-      <c r="C161" s="7" t="s">
+      <c r="B161" s="6">
+        <v>10</v>
+      </c>
+      <c r="C161" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="D161" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E161" s="7"/>
-      <c r="F161" s="7" t="s">
+      <c r="E161" s="6"/>
+      <c r="F161" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="A162" s="7" t="s">
+    <row r="162" spans="1:8">
+      <c r="A162" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B162" s="7">
-        <v>10</v>
-      </c>
-      <c r="C162" s="7" t="s">
+      <c r="B162" s="6">
+        <v>10</v>
+      </c>
+      <c r="C162" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D162" s="7" t="s">
+      <c r="D162" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7" t="s">
+      <c r="E162" s="6"/>
+      <c r="F162" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="A163" s="7" t="s">
+    <row r="163" spans="1:8">
+      <c r="A163" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B163" s="7">
-        <v>10</v>
-      </c>
-      <c r="C163" s="7" t="s">
+      <c r="B163" s="6">
+        <v>10</v>
+      </c>
+      <c r="C163" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D163" s="7" t="s">
+      <c r="D163" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7" t="s">
+      <c r="E163" s="6"/>
+      <c r="F163" s="6" t="s">
         <v>228</v>
       </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H166" s="6"/>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B167" s="6">
+        <v>1</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H167" s="6"/>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B168" s="6">
+        <v>1</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D168" s="6"/>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+      <c r="G168" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H168" s="6"/>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B169" s="6">
+        <v>1</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D169" s="6"/>
+      <c r="E169" s="6"/>
+      <c r="F169" s="6"/>
+      <c r="G169" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H169" s="6"/>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B170" s="6">
+        <v>2</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D170" s="6"/>
+      <c r="E170" s="6"/>
+      <c r="F170" s="6"/>
+      <c r="G170" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H170" s="6"/>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B171" s="6">
+        <v>1</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D171" s="6"/>
+      <c r="E171" s="6"/>
+      <c r="F171" s="6"/>
+      <c r="G171" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H171" s="6"/>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B172" s="6">
+        <v>2</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6"/>
+      <c r="F172" s="6"/>
+      <c r="G172" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H172" s="6"/>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B173" s="6">
+        <v>2</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D173" s="6"/>
+      <c r="E173" s="6"/>
+      <c r="F173" s="6"/>
+      <c r="G173" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H173" s="6"/>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B174" s="6">
+        <v>2</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D174" s="6"/>
+      <c r="E174" s="6"/>
+      <c r="F174" s="6"/>
+      <c r="G174" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H174" s="6"/>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B175" s="6">
+        <v>1</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6"/>
+      <c r="G175" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H175" s="6"/>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B176" s="6">
+        <v>1</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H176" s="6"/>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B177" s="6">
+        <v>1</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
+      <c r="F177" s="6"/>
+      <c r="G177" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H177" s="6"/>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B178" s="6">
+        <v>1</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D178" s="6"/>
+      <c r="E178" s="6"/>
+      <c r="F178" s="6"/>
+      <c r="G178" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H178" s="6"/>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B179" s="6">
+        <v>2</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6"/>
+      <c r="G179" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H179" s="6"/>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B180" s="6">
+        <v>1</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
+      <c r="F180" s="6"/>
+      <c r="G180" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H180" s="6"/>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B181" s="6">
+        <v>1</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6"/>
+      <c r="G181" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H181" s="6"/>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B182" s="6">
+        <v>1</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D182" s="6"/>
+      <c r="E182" s="6"/>
+      <c r="F182" s="6"/>
+      <c r="G182" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H182" s="6"/>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B183" s="6">
+        <v>1</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
+      <c r="F183" s="6"/>
+      <c r="G183" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H183" s="6"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B184" s="6">
+        <v>1</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D184" s="6"/>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6"/>
+      <c r="G184" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H184" s="6"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B185" s="6">
+        <v>1</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D185" s="6"/>
+      <c r="E185" s="6"/>
+      <c r="F185" s="6"/>
+      <c r="G185" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H185" s="6"/>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B186" s="6">
+        <v>1</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D186" s="6"/>
+      <c r="E186" s="6"/>
+      <c r="F186" s="6"/>
+      <c r="G186" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H186" s="6"/>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B187" s="6">
+        <v>1</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D187" s="6"/>
+      <c r="E187" s="6"/>
+      <c r="F187" s="6"/>
+      <c r="G187" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H187" s="6"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B188" s="6">
+        <v>1</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D188" s="6"/>
+      <c r="E188" s="6"/>
+      <c r="F188" s="6"/>
+      <c r="G188" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H188" s="6"/>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B189" s="6">
+        <v>1</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D189" s="6"/>
+      <c r="E189" s="6"/>
+      <c r="F189" s="6"/>
+      <c r="G189" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H189" s="6"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B190" s="6">
+        <v>1</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D190" s="6"/>
+      <c r="E190" s="6"/>
+      <c r="F190" s="6"/>
+      <c r="G190" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H190" s="6"/>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B191" s="6">
+        <v>1</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D191" s="6"/>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6"/>
+      <c r="G191" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H191" s="6"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B192" s="6">
+        <v>1</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D192" s="6"/>
+      <c r="E192" s="6"/>
+      <c r="F192" s="6"/>
+      <c r="G192" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H192" s="6"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B193" s="6">
+        <v>1</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D193" s="6"/>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
+      <c r="G193" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H193" s="6"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B194" s="6">
+        <v>2</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D194" s="6"/>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6"/>
+      <c r="G194" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H194" s="6"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B195" s="6">
+        <v>1</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+      <c r="G195" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H195" s="6"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B196" s="6">
+        <v>1</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6"/>
+      <c r="G196" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H196" s="6"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B197" s="6">
+        <v>5</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D197" s="6"/>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6"/>
+      <c r="G197" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H197" s="6"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B198" s="6">
+        <v>5</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="D198" s="6"/>
+      <c r="E198" s="6"/>
+      <c r="F198" s="6"/>
+      <c r="G198" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H198" s="6"/>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B199" s="6">
+        <v>5</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D199" s="6"/>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6"/>
+      <c r="G199" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H199" s="6"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B200" s="6">
+        <v>5</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6"/>
+      <c r="G200" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H200" s="6"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B201" s="6">
+        <v>5</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
+      <c r="F201" s="6"/>
+      <c r="G201" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H201" s="6"/>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B202" s="6">
+        <v>5</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
+      <c r="F202" s="6"/>
+      <c r="G202" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H202" s="6"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B203" s="6">
+        <v>5</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6"/>
+      <c r="G203" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H203" s="6"/>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B204" s="6">
+        <v>5</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="6"/>
+      <c r="G204" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H204" s="6"/>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B205" s="6">
+        <v>5</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D205" s="6"/>
+      <c r="E205" s="6"/>
+      <c r="F205" s="6"/>
+      <c r="G205" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H205" s="6"/>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B206" s="6">
+        <v>5</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D206" s="6"/>
+      <c r="E206" s="6"/>
+      <c r="F206" s="6"/>
+      <c r="G206" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H206" s="6"/>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B207" s="6">
+        <v>5</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D207" s="6"/>
+      <c r="E207" s="6"/>
+      <c r="F207" s="6"/>
+      <c r="G207" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H207" s="6"/>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B208" s="6">
+        <v>5</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D208" s="6"/>
+      <c r="E208" s="6"/>
+      <c r="F208" s="6"/>
+      <c r="G208" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H208" s="6"/>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B209" s="6">
+        <v>5</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="D209" s="6"/>
+      <c r="E209" s="6"/>
+      <c r="F209" s="6"/>
+      <c r="G209" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H209" s="6"/>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B210" s="6">
+        <v>5</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D210" s="6"/>
+      <c r="E210" s="6"/>
+      <c r="F210" s="6"/>
+      <c r="G210" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H210" s="6"/>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B211" s="6">
+        <v>5</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="D211" s="6"/>
+      <c r="E211" s="6"/>
+      <c r="F211" s="6"/>
+      <c r="G211" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H211" s="6"/>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B212" s="6">
+        <v>5</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
+      <c r="F212" s="6"/>
+      <c r="G212" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H212" s="6"/>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B213" s="6">
+        <v>5</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
+      <c r="F213" s="6"/>
+      <c r="G213" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H213" s="6"/>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B214" s="6">
+        <v>5</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D214" s="6"/>
+      <c r="E214" s="6"/>
+      <c r="F214" s="6"/>
+      <c r="G214" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H214" s="6"/>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B215" s="6">
+        <v>5</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+      <c r="F215" s="6"/>
+      <c r="G215" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H215" s="6"/>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B216" s="6">
+        <v>5</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D216" s="6"/>
+      <c r="E216" s="6"/>
+      <c r="F216" s="6"/>
+      <c r="G216" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H216" s="6"/>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B217" s="6">
+        <v>1</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D217" s="6"/>
+      <c r="E217" s="6"/>
+      <c r="F217" s="6"/>
+      <c r="G217" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H217" s="6"/>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B218" s="6">
+        <v>1</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
+      <c r="F218" s="6"/>
+      <c r="G218" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H218" s="6"/>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B219" s="6">
+        <v>2</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
+      <c r="F219" s="6"/>
+      <c r="G219" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H219" s="6"/>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B220" s="6">
+        <v>1</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D220" s="6"/>
+      <c r="E220" s="6"/>
+      <c r="F220" s="6"/>
+      <c r="G220" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H220" s="6"/>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B221" s="6">
+        <v>2</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D221" s="6"/>
+      <c r="E221" s="6"/>
+      <c r="F221" s="6"/>
+      <c r="G221" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H221" s="6"/>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B222" s="6">
+        <v>2</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D222" s="6"/>
+      <c r="E222" s="6"/>
+      <c r="F222" s="6"/>
+      <c r="G222" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H222" s="6"/>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="B223" s="6">
+        <v>2</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D223" s="6"/>
+      <c r="E223" s="6"/>
+      <c r="F223" s="6"/>
+      <c r="G223" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H223" s="6"/>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B224" s="6">
+        <v>2</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="D224" s="6"/>
+      <c r="E224" s="6"/>
+      <c r="F224" s="6"/>
+      <c r="G224" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H224" s="6"/>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="B225" s="6">
+        <v>2</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D225" s="6"/>
+      <c r="E225" s="6"/>
+      <c r="F225" s="6"/>
+      <c r="G225" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H225" s="6"/>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B226" s="6">
+        <v>2</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D226" s="6"/>
+      <c r="E226" s="6"/>
+      <c r="F226" s="6"/>
+      <c r="G226" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H226" s="6"/>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B227" s="6">
+        <v>2</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D227" s="6"/>
+      <c r="E227" s="6"/>
+      <c r="F227" s="6"/>
+      <c r="G227" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H227" s="6"/>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B228" s="6">
+        <v>2</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D228" s="6"/>
+      <c r="E228" s="6"/>
+      <c r="F228" s="6"/>
+      <c r="G228" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H228" s="6"/>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B229" s="6">
+        <v>2</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D229" s="6"/>
+      <c r="E229" s="6"/>
+      <c r="F229" s="6"/>
+      <c r="G229" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H229" s="6"/>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B230" s="6">
+        <v>2</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D230" s="6"/>
+      <c r="E230" s="6"/>
+      <c r="F230" s="6"/>
+      <c r="G230" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H230" s="6"/>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="B231" s="6">
+        <v>2</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D231" s="6"/>
+      <c r="E231" s="6"/>
+      <c r="F231" s="6"/>
+      <c r="G231" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H231" s="6"/>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B232" s="6">
+        <v>2</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D232" s="6"/>
+      <c r="E232" s="6"/>
+      <c r="F232" s="6"/>
+      <c r="G232" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H232" s="6"/>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B233" s="6">
+        <v>1</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D233" s="6"/>
+      <c r="E233" s="6"/>
+      <c r="F233" s="6"/>
+      <c r="G233" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H233" s="6"/>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B234" s="6">
+        <v>3</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D234" s="6"/>
+      <c r="E234" s="6"/>
+      <c r="F234" s="6"/>
+      <c r="G234" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H234" s="6"/>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B235" s="6">
+        <v>3</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D235" s="6"/>
+      <c r="E235" s="6"/>
+      <c r="F235" s="6"/>
+      <c r="G235" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H235" s="6"/>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B236" s="6">
+        <v>1</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D236" s="6"/>
+      <c r="E236" s="6"/>
+      <c r="F236" s="6"/>
+      <c r="G236" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H236" s="6"/>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B237" s="6">
+        <v>1</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D237" s="6"/>
+      <c r="E237" s="6"/>
+      <c r="F237" s="6"/>
+      <c r="G237" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H237" s="6"/>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B238" s="6">
+        <v>1</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D238" s="6"/>
+      <c r="E238" s="6"/>
+      <c r="F238" s="6"/>
+      <c r="G238" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H238" s="6"/>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B239" s="6">
+        <v>1</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D239" s="6"/>
+      <c r="E239" s="6"/>
+      <c r="F239" s="6"/>
+      <c r="G239" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H239" s="6"/>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B240" s="6">
+        <v>2</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D240" s="6"/>
+      <c r="E240" s="6"/>
+      <c r="F240" s="6"/>
+      <c r="G240" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H240" s="6"/>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B241" s="6">
+        <v>2</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D241" s="6"/>
+      <c r="E241" s="6"/>
+      <c r="F241" s="6"/>
+      <c r="G241" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H241" s="6"/>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B242" s="6">
+        <v>1</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D242" s="6"/>
+      <c r="E242" s="6"/>
+      <c r="F242" s="6"/>
+      <c r="G242" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H242" s="6"/>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B243" s="6">
+        <v>1</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D243" s="6"/>
+      <c r="E243" s="6"/>
+      <c r="F243" s="6"/>
+      <c r="G243" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H243" s="6"/>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B244" s="6">
+        <v>1</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D244" s="6"/>
+      <c r="E244" s="6"/>
+      <c r="F244" s="6"/>
+      <c r="G244" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H244" s="6"/>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B245" s="6">
+        <v>1</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D245" s="6"/>
+      <c r="E245" s="6"/>
+      <c r="F245" s="6"/>
+      <c r="G245" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H245" s="6"/>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B246" s="6">
+        <v>2</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D246" s="6"/>
+      <c r="E246" s="6"/>
+      <c r="F246" s="6"/>
+      <c r="G246" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H246" s="6"/>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B247" s="6">
+        <v>2</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D247" s="6"/>
+      <c r="E247" s="6"/>
+      <c r="F247" s="6"/>
+      <c r="G247" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H247" s="6"/>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B248" s="6">
+        <v>2</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D248" s="6"/>
+      <c r="E248" s="6"/>
+      <c r="F248" s="6"/>
+      <c r="G248" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H248" s="6"/>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B249" s="6">
+        <v>1</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D249" s="6"/>
+      <c r="E249" s="6"/>
+      <c r="F249" s="6"/>
+      <c r="G249" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H249" s="6"/>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B250" s="6">
+        <v>1</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D250" s="6"/>
+      <c r="E250" s="6"/>
+      <c r="F250" s="6"/>
+      <c r="G250" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H250" s="6"/>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B251" s="6">
+        <v>1</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D251" s="6"/>
+      <c r="E251" s="6"/>
+      <c r="F251" s="6"/>
+      <c r="G251" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H251" s="6"/>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B252" s="6">
+        <v>1</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="D252" s="6"/>
+      <c r="E252" s="6"/>
+      <c r="F252" s="6"/>
+      <c r="G252" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H252" s="6"/>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B253" s="6">
+        <v>1</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="D253" s="6"/>
+      <c r="E253" s="6"/>
+      <c r="F253" s="6"/>
+      <c r="G253" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H253" s="6"/>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B254" s="6">
+        <v>4</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="D254" s="6"/>
+      <c r="E254" s="6"/>
+      <c r="F254" s="6"/>
+      <c r="G254" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H254" s="6"/>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B255" s="6">
+        <v>2</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D255" s="6"/>
+      <c r="E255" s="6"/>
+      <c r="F255" s="6"/>
+      <c r="G255" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H255" s="6"/>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B256" s="6">
+        <v>2</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D256" s="6"/>
+      <c r="E256" s="6"/>
+      <c r="F256" s="6"/>
+      <c r="G256" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H256" s="6"/>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B257" s="6">
+        <v>2</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D257" s="6"/>
+      <c r="E257" s="6"/>
+      <c r="F257" s="6"/>
+      <c r="G257" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H257" s="6"/>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B258" s="6">
+        <v>2</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D258" s="6"/>
+      <c r="E258" s="6"/>
+      <c r="F258" s="6"/>
+      <c r="G258" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H258" s="6"/>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B259" s="6">
+        <v>2</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D259" s="6"/>
+      <c r="E259" s="6"/>
+      <c r="F259" s="6"/>
+      <c r="G259" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H259" s="6"/>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B260" s="6">
+        <v>1</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D260" s="6"/>
+      <c r="E260" s="6"/>
+      <c r="F260" s="6"/>
+      <c r="G260" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H260" s="6"/>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B261" s="6">
+        <v>1</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D261" s="6"/>
+      <c r="E261" s="6"/>
+      <c r="F261" s="6"/>
+      <c r="G261" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H261" s="6"/>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B262" s="6">
+        <v>1</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D262" s="6"/>
+      <c r="E262" s="6"/>
+      <c r="F262" s="6"/>
+      <c r="G262" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H262" s="6"/>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B263" s="6">
+        <v>1</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="D263" s="6"/>
+      <c r="E263" s="6"/>
+      <c r="F263" s="6"/>
+      <c r="G263" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H263" s="6"/>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B264" s="6">
+        <v>1</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D264" s="6"/>
+      <c r="E264" s="6"/>
+      <c r="F264" s="6"/>
+      <c r="G264" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H264" s="6"/>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B265" s="6">
+        <v>1</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="D265" s="6"/>
+      <c r="E265" s="6"/>
+      <c r="F265" s="6"/>
+      <c r="G265" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H265" s="6"/>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B266" s="6">
+        <v>1</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D266" s="6"/>
+      <c r="E266" s="6"/>
+      <c r="F266" s="6"/>
+      <c r="G266" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H266" s="6"/>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B267" s="6">
+        <v>45</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D267" s="6"/>
+      <c r="E267" s="6"/>
+      <c r="F267" s="6"/>
+      <c r="G267" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H267" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
